--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_46.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5780594.528090313</v>
+        <v>5740253.269252241</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645786</v>
+        <v>6767152.31864579</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645786</v>
+        <v>6767152.31864579</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517474</v>
+        <v>2916902.906517475</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517474</v>
+        <v>2916902.906517475</v>
       </c>
     </row>
     <row r="11">
@@ -660,7 +660,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>351.4978904062576</v>
+        <v>351.4978904062565</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -681,7 +681,7 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>97.12488247690061</v>
+        <v>814</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
@@ -693,19 +693,19 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O2" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>313.1545016101228</v>
       </c>
       <c r="Q2" t="n">
-        <v>587.0002301911333</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
         <v>586.6755817285639</v>
@@ -717,7 +717,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>638.3734759809475</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
         <v>192.2818334606677</v>
@@ -742,16 +742,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>16.23472619600306</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -787,7 +787,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>5.357765217513816</v>
+        <v>130.9153024145154</v>
       </c>
       <c r="U3" t="n">
         <v>0.2103597601867477</v>
@@ -796,7 +796,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>120.6316114025499</v>
+        <v>91.42153354831642</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>320.9396782847063</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -906,7 +906,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
         <v>408.0096587035274</v>
@@ -915,28 +915,28 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>97.12488247690055</v>
+        <v>814</v>
       </c>
       <c r="L5" t="n">
-        <v>814</v>
+        <v>700.3237126680341</v>
       </c>
       <c r="M5" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N5" t="n">
-        <v>814</v>
+        <v>194.5855355810509</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>31.55202437320305</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>370.9706110579117</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>109.7879374857201</v>
+        <v>323.5464468474237</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617061031</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>297.3920501269273</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1134,31 +1134,31 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>351.4978904062571</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>97.12488247690055</v>
+        <v>814</v>
       </c>
       <c r="L8" t="n">
-        <v>650.9664887921559</v>
+        <v>313.1545016101228</v>
       </c>
       <c r="M8" t="n">
         <v>297.9910820919849</v>
@@ -1176,7 +1176,7 @@
         <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
@@ -1188,13 +1188,13 @@
         <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>592.2818334606677</v>
+        <v>284.8914663351031</v>
       </c>
       <c r="Y8" t="n">
         <v>111.3174326828064</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>109.7879374857201</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>93.03180718248363</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>224.4745782429939</v>
@@ -1422,16 +1422,16 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>422.567398547346</v>
       </c>
       <c r="V11" t="n">
-        <v>292.914605660466</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>286.3174326828064</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1562,13 +1562,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>230.5861999910206</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -1611,16 +1611,16 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
         <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>70.69971198282684</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>335.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>398.2212965486107</v>
@@ -1665,7 +1665,7 @@
         <v>378.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>387.3734759809475</v>
+        <v>330.6184490949257</v>
       </c>
       <c r="X14" t="n">
         <v>341.2818334606677</v>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1790,25 +1790,25 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>14.12259707819939</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.97841917455702</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>170.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>130.9085471252638</v>
+        <v>131.3391557398498</v>
       </c>
       <c r="E17" t="n">
         <v>125.3632896068686</v>
@@ -1857,7 +1857,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H17" t="n">
-        <v>129.0096587035274</v>
+        <v>128.5790500889414</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2027,28 +2027,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>144.5476281577792</v>
+        <v>16.34743437468335</v>
       </c>
       <c r="M19" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>24.50310124710636</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>125.8896287080119</v>
+        <v>125.4590200934799</v>
       </c>
       <c r="G20" t="n">
         <v>124.7573722870162</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>215.4175591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>338.6387678008247</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>202.9993129555745</v>
+        <v>202.5687043409885</v>
       </c>
       <c r="C23" t="n">
         <v>170.4745782429939</v>
@@ -2331,7 +2331,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>128.5790500890098</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>339.4016293563777</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2553,22 +2553,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>189.411675845388</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>59.8121514084191</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2610,10 +2610,10 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>367.2818334606677</v>
@@ -2714,10 +2714,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>25.71204843823643</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2793,16 +2793,16 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>14.21404555647561</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>234.7852654047167</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
@@ -2850,7 +2850,7 @@
         <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>367.2818334606677</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>45.14518808597777</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>283.8069350917773</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3048,28 +3048,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>757.6173000000412</v>
+        <v>757.6173000000402</v>
       </c>
       <c r="K32" t="n">
-        <v>10.23281455287229</v>
+        <v>10.23281455289469</v>
       </c>
       <c r="L32" t="n">
-        <v>564.0482340938205</v>
+        <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000421</v>
+        <v>256.9910820920259</v>
       </c>
       <c r="N32" t="n">
-        <v>153.5855355810893</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>115.2893765249682</v>
       </c>
       <c r="Q32" t="n">
-        <v>757.6173000000409</v>
+        <v>329.9706110579529</v>
       </c>
       <c r="R32" t="n">
         <v>8.456591385414804</v>
@@ -3218,19 +3218,19 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>108.4418998849671</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>194.5984637871032</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3282,34 +3282,34 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I35" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>377.7382696589829</v>
+        <v>377.738269658982</v>
       </c>
       <c r="K35" t="n">
-        <v>772.9999999999999</v>
+        <v>10.23281455292829</v>
       </c>
       <c r="L35" t="n">
         <v>773</v>
       </c>
       <c r="M35" t="n">
-        <v>654.6988358539371</v>
+        <v>256.9910820920331</v>
       </c>
       <c r="N35" t="n">
-        <v>107.693467657093</v>
+        <v>153.5855355810957</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>341.5828712849518</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.970611057961</v>
+        <v>329.9706110579601</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S35" t="n">
         <v>203.8481678023229</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -3464,13 +3464,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>300.9686893526101</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>435.6021279811511</v>
+        <v>225.4675834971127</v>
       </c>
       <c r="S37" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
         <v>119.3391557398498</v>
       </c>
       <c r="E38" t="n">
-        <v>113.3632896068686</v>
+        <v>121.8198809922829</v>
       </c>
       <c r="F38" t="n">
         <v>113.8896287080119</v>
@@ -3519,31 +3519,31 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I38" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>377.7382696589902</v>
+        <v>377.7382696589893</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320760155</v>
+        <v>10.2328145528275</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920413</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355811038</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>397.7077537619157</v>
+        <v>324.5128000159598</v>
       </c>
       <c r="Q38" t="n">
-        <v>329.9706110579683</v>
+        <v>757.6173000000545</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3692,22 +3692,22 @@
         <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>226.7541306595264</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>181.8647883057893</v>
       </c>
       <c r="S40" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>197.3391557398498</v>
@@ -3747,13 +3747,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,13 +3783,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>341.0002902217254</v>
+        <v>105.4649181164947</v>
       </c>
       <c r="U41" t="n">
         <v>436.2212965486107</v>
@@ -3798,7 +3798,7 @@
         <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>425.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>379.2818334606677</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>171.5565566463266</v>
+        <v>14.70514898422604</v>
       </c>
       <c r="C42" t="n">
         <v>148.0999124455193</v>
@@ -3826,7 +3826,7 @@
         <v>129.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>126.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>112.7395358750273</v>
@@ -3865,7 +3865,7 @@
         <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>253.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>192.3577652175138</v>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>32.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>15.77112610161862</v>
@@ -3941,10 +3941,10 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>23.68833188166164</v>
+        <v>271.3436093272373</v>
       </c>
       <c r="S43" t="n">
-        <v>149.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>13.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>39.27646703307393</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>142.4109888009625</v>
+        <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>221.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>307.8481678023229</v>
@@ -4029,7 +4029,7 @@
         <v>399.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>462.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>442.8510241668239</v>
@@ -4038,10 +4038,10 @@
         <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>324.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4054,13 +4054,13 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>32.00376094464704</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>152.6362423378769</v>
@@ -4072,7 +4072,7 @@
         <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>30.12638589134853</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>279.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
@@ -4114,13 +4114,13 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>232.8627394453875</v>
+        <v>162.7594696020988</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>212.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1049.365529973417</v>
+        <v>1049.365529973416</v>
       </c>
       <c r="C2" t="n">
-        <v>999.3912085158472</v>
+        <v>999.3912085158463</v>
       </c>
       <c r="D2" t="n">
-        <v>988.9476168594333</v>
+        <v>584.9072128190282</v>
       </c>
       <c r="E2" t="n">
-        <v>984.5402536201721</v>
+        <v>580.499849579767</v>
       </c>
       <c r="F2" t="n">
-        <v>979.6012347231904</v>
+        <v>575.5608306827853</v>
       </c>
       <c r="G2" t="n">
-        <v>571.7655051403457</v>
+        <v>571.7655051403447</v>
       </c>
       <c r="H2" t="n">
         <v>216.7171309926107</v>
@@ -4324,22 +4324,22 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>1155.766108953703</v>
+        <v>431.6498286273397</v>
       </c>
       <c r="L2" t="n">
-        <v>1139.40388673148</v>
+        <v>415.2876064051174</v>
       </c>
       <c r="M2" t="n">
-        <v>1644.262793709273</v>
+        <v>920.1465133829104</v>
       </c>
       <c r="N2" t="n">
-        <v>2253.571747667811</v>
+        <v>1529.455467341449</v>
       </c>
       <c r="O2" t="n">
-        <v>2237.209525445589</v>
+        <v>2335.315467341449</v>
       </c>
       <c r="P2" t="n">
-        <v>3043.069525445589</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q2" t="n">
         <v>3256</v>
@@ -4348,19 +4348,19 @@
         <v>3256</v>
       </c>
       <c r="S2" t="n">
-        <v>3160.193769896644</v>
+        <v>2756.153365856239</v>
       </c>
       <c r="T2" t="n">
-        <v>2567.592172191024</v>
+        <v>2163.551768150619</v>
       </c>
       <c r="U2" t="n">
-        <v>2315.853488808589</v>
+        <v>1911.813084768184</v>
       </c>
       <c r="V2" t="n">
-        <v>2083.680737124928</v>
+        <v>1679.640333084523</v>
       </c>
       <c r="W2" t="n">
-        <v>1438.85904421488</v>
+        <v>1438.859044214879</v>
       </c>
       <c r="X2" t="n">
         <v>1244.634970012185</v>
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>756.6819790837809</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="C3" t="n">
-        <v>756.6819790837809</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="D3" t="n">
-        <v>756.6819790837809</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="E3" t="n">
-        <v>410.5485475464954</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="F3" t="n">
-        <v>410.5485475464954</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="G3" t="n">
-        <v>81.51871332929602</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="H3" t="n">
         <v>65.12</v>
@@ -4421,31 +4421,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1045.724879873102</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>896.9634684666578</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>829.7271048660403</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>824.3152208079456</v>
+        <v>872.3169661548932</v>
       </c>
       <c r="U3" t="n">
-        <v>824.1027362016963</v>
+        <v>872.1044815486439</v>
       </c>
       <c r="V3" t="n">
-        <v>809.4454966143022</v>
+        <v>857.4472419612498</v>
       </c>
       <c r="W3" t="n">
-        <v>776.7453522609401</v>
+        <v>420.7066935674835</v>
       </c>
       <c r="X3" t="n">
-        <v>756.6819790837809</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="Y3" t="n">
-        <v>756.6819790837809</v>
+        <v>400.6433203903244</v>
       </c>
     </row>
     <row r="4">
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>774.1727458004956</v>
+        <v>476.567684463691</v>
       </c>
       <c r="C4" t="n">
-        <v>774.1727458004956</v>
+        <v>536.4926290835506</v>
       </c>
       <c r="D4" t="n">
-        <v>774.1727458004956</v>
+        <v>649.8117732085507</v>
       </c>
       <c r="E4" t="n">
-        <v>892.0016500119086</v>
+        <v>767.6406774199637</v>
       </c>
       <c r="F4" t="n">
-        <v>892.0016500119086</v>
+        <v>892.0016500118992</v>
       </c>
       <c r="G4" t="n">
-        <v>1045.408215898794</v>
+        <v>1045.408215898784</v>
       </c>
       <c r="H4" t="n">
-        <v>1214.924801058192</v>
+        <v>1214.924801058182</v>
       </c>
       <c r="I4" t="n">
-        <v>1436.057679994275</v>
+        <v>1436.057679994265</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994275</v>
+        <v>1436.057679994265</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931133</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931143</v>
+        <v>1522.636630943478</v>
       </c>
       <c r="M4" t="n">
-        <v>1424.572001403315</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1251.657783957168</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O4" t="n">
-        <v>1008.783476806648</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P4" t="n">
-        <v>718.4320653639438</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>389.3014932168751</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
@@ -4509,22 +4509,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>290.445934252978</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U4" t="n">
-        <v>536.9971268912645</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="V4" t="n">
-        <v>735.8185197772104</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="W4" t="n">
-        <v>774.1727458004956</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="X4" t="n">
-        <v>774.1727458004956</v>
+        <v>253.4010461183667</v>
       </c>
       <c r="Y4" t="n">
-        <v>774.1727458004956</v>
+        <v>364.8103467973989</v>
       </c>
     </row>
     <row r="5">
@@ -4537,16 +4537,16 @@
         <v>1106.448124213083</v>
       </c>
       <c r="C5" t="n">
-        <v>1056.473802755514</v>
+        <v>652.4333987151097</v>
       </c>
       <c r="D5" t="n">
-        <v>1046.0302110991</v>
+        <v>641.9898070586958</v>
       </c>
       <c r="E5" t="n">
-        <v>1041.622847859838</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F5" t="n">
-        <v>1036.683828962857</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G5" t="n">
         <v>628.8480993800122</v>
@@ -4558,25 +4558,25 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K5" t="n">
-        <v>772.8740581041409</v>
+        <v>431.6498286273397</v>
       </c>
       <c r="L5" t="n">
-        <v>756.5118358819186</v>
+        <v>530.1121390636688</v>
       </c>
       <c r="M5" t="n">
-        <v>1261.370742859712</v>
+        <v>1034.971046041462</v>
       </c>
       <c r="N5" t="n">
-        <v>1245.008520637489</v>
+        <v>1644.28</v>
       </c>
       <c r="O5" t="n">
-        <v>2050.868520637489</v>
+        <v>2450.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2824.857788947385</v>
+        <v>3256</v>
       </c>
       <c r="Q5" t="n">
         <v>3256</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>527.4691155388109</v>
+        <v>756.6819790837809</v>
       </c>
       <c r="C6" t="n">
-        <v>527.4691155388109</v>
+        <v>391.9345927751755</v>
       </c>
       <c r="D6" t="n">
-        <v>176.0169065512325</v>
+        <v>391.9345927751755</v>
       </c>
       <c r="E6" t="n">
-        <v>176.0169065512325</v>
+        <v>391.9345927751755</v>
       </c>
       <c r="F6" t="n">
-        <v>176.0169065512325</v>
+        <v>391.9345927751755</v>
       </c>
       <c r="G6" t="n">
-        <v>176.0169065512325</v>
+        <v>391.9345927751755</v>
       </c>
       <c r="H6" t="n">
         <v>65.12</v>
@@ -4658,31 +4658,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1220.552420368536</v>
+        <v>1045.724879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1071.791008962092</v>
+        <v>896.9634684666578</v>
       </c>
       <c r="S6" t="n">
-        <v>1004.554645361474</v>
+        <v>829.7271048660403</v>
       </c>
       <c r="T6" t="n">
-        <v>999.1427613033796</v>
+        <v>824.3152208079456</v>
       </c>
       <c r="U6" t="n">
-        <v>998.9302766971304</v>
+        <v>824.1027362016963</v>
       </c>
       <c r="V6" t="n">
-        <v>984.2730371097363</v>
+        <v>809.4454966143022</v>
       </c>
       <c r="W6" t="n">
-        <v>951.5728927563741</v>
+        <v>776.7453522609401</v>
       </c>
       <c r="X6" t="n">
-        <v>527.4691155388109</v>
+        <v>756.6819790837809</v>
       </c>
       <c r="Y6" t="n">
-        <v>527.4691155388109</v>
+        <v>756.6819790837809</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>410.4906232651246</v>
+        <v>897.9928839078791</v>
       </c>
       <c r="C7" t="n">
-        <v>536.4926290835604</v>
+        <v>897.9928839078791</v>
       </c>
       <c r="D7" t="n">
-        <v>649.8117732085605</v>
+        <v>897.9928839078791</v>
       </c>
       <c r="E7" t="n">
-        <v>767.6406774199735</v>
+        <v>1015.821788119292</v>
       </c>
       <c r="F7" t="n">
-        <v>892.001650011909</v>
+        <v>1015.821788119292</v>
       </c>
       <c r="G7" t="n">
-        <v>1045.408215898794</v>
+        <v>1015.821788119292</v>
       </c>
       <c r="H7" t="n">
-        <v>1214.924801058192</v>
+        <v>1185.33837327869</v>
       </c>
       <c r="I7" t="n">
-        <v>1436.057679994275</v>
+        <v>1185.33837327869</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994275</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="L7" t="n">
-        <v>1522.636630943487</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="M7" t="n">
-        <v>1400.786518415659</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1227.872300969513</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O7" t="n">
-        <v>984.9979938189928</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P7" t="n">
-        <v>694.6465823762883</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>365.5160102292195</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T7" t="n">
-        <v>290.445934252978</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="U7" t="n">
-        <v>410.4906232651246</v>
+        <v>499.7468717970915</v>
       </c>
       <c r="V7" t="n">
-        <v>410.4906232651246</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="W7" t="n">
-        <v>410.4906232651246</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="X7" t="n">
-        <v>410.4906232651246</v>
+        <v>786.5835832288468</v>
       </c>
       <c r="Y7" t="n">
-        <v>410.4906232651246</v>
+        <v>897.9928839078791</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1049.365529973416</v>
+        <v>1510.488528253487</v>
       </c>
       <c r="C8" t="n">
-        <v>999.3912085158468</v>
+        <v>1460.514206795918</v>
       </c>
       <c r="D8" t="n">
-        <v>988.9476168594329</v>
+        <v>1046.0302110991</v>
       </c>
       <c r="E8" t="n">
-        <v>984.5402536201716</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F8" t="n">
-        <v>979.6012347231899</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G8" t="n">
-        <v>571.7655051403452</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4795,10 +4795,10 @@
         <v>65.12</v>
       </c>
       <c r="J8" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>772.8740581041409</v>
+        <v>431.6498286273397</v>
       </c>
       <c r="L8" t="n">
         <v>921.1921502332762</v>
@@ -4819,28 +4819,28 @@
         <v>3256</v>
       </c>
       <c r="R8" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>3160.193769896644</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T8" t="n">
-        <v>2971.632576231427</v>
+        <v>2718.219850142241</v>
       </c>
       <c r="U8" t="n">
-        <v>2719.893892848992</v>
+        <v>2466.481166759806</v>
       </c>
       <c r="V8" t="n">
-        <v>2083.680737124928</v>
+        <v>2234.308415076146</v>
       </c>
       <c r="W8" t="n">
-        <v>1842.899448255284</v>
+        <v>1993.527126206502</v>
       </c>
       <c r="X8" t="n">
-        <v>1244.634970012185</v>
+        <v>1705.757968292256</v>
       </c>
       <c r="Y8" t="n">
-        <v>1132.193118817431</v>
+        <v>1593.316117097502</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.12</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12</v>
+        <v>416.5722089875784</v>
       </c>
       <c r="D9" t="n">
         <v>65.12</v>
@@ -4910,16 +4910,16 @@
         <v>998.9302766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>984.2730371097363</v>
+        <v>580.2326330693322</v>
       </c>
       <c r="W9" t="n">
-        <v>547.53248871597</v>
+        <v>547.5324887159701</v>
       </c>
       <c r="X9" t="n">
-        <v>453.5609663094208</v>
+        <v>527.4691155388109</v>
       </c>
       <c r="Y9" t="n">
-        <v>453.5609663094208</v>
+        <v>527.4691155388109</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>659.500178284698</v>
+        <v>810.0297405151414</v>
       </c>
       <c r="C10" t="n">
-        <v>785.5021841031338</v>
+        <v>936.0317463335772</v>
       </c>
       <c r="D10" t="n">
-        <v>803.2183390954431</v>
+        <v>1049.350890458577</v>
       </c>
       <c r="E10" t="n">
-        <v>921.0472433068561</v>
+        <v>1049.350890458577</v>
       </c>
       <c r="F10" t="n">
-        <v>1045.408215898792</v>
+        <v>1049.350890458577</v>
       </c>
       <c r="G10" t="n">
-        <v>1045.408215898792</v>
+        <v>1202.757456345463</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.924801058189</v>
+        <v>1372.27404150486</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994272</v>
+        <v>1372.27404150486</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994272</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="K10" t="n">
         <v>1546.422113931141</v>
@@ -4980,25 +4980,25 @@
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T10" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="U10" t="n">
-        <v>348.9214477324598</v>
+        <v>65.12</v>
       </c>
       <c r="V10" t="n">
-        <v>547.7428406184058</v>
+        <v>263.941392885946</v>
       </c>
       <c r="W10" t="n">
-        <v>547.7428406184058</v>
+        <v>435.8323111456234</v>
       </c>
       <c r="X10" t="n">
-        <v>547.7428406184058</v>
+        <v>586.8631021698169</v>
       </c>
       <c r="Y10" t="n">
-        <v>547.7428406184058</v>
+        <v>698.2724028488492</v>
       </c>
     </row>
     <row r="11">
@@ -5035,19 +5035,19 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>887.4717564436343</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>1693.331756443634</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>2204.180585172569</v>
+        <v>967.2779417665907</v>
       </c>
       <c r="N11" t="n">
-        <v>2817.400904947332</v>
+        <v>1580.498261541354</v>
       </c>
       <c r="O11" t="n">
-        <v>2817.400904947332</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P11" t="n">
         <v>2817.400904947332</v>
@@ -5065,19 +5065,19 @@
         <v>2591.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2163.450863729503</v>
+        <v>2165.121467771185</v>
       </c>
       <c r="V11" t="n">
-        <v>1867.577524678527</v>
+        <v>1756.181039319847</v>
       </c>
       <c r="W11" t="n">
-        <v>1867.577524678527</v>
+        <v>1756.181039319847</v>
       </c>
       <c r="X11" t="n">
-        <v>1496.585773708156</v>
+        <v>1756.181039319847</v>
       </c>
       <c r="Y11" t="n">
-        <v>1207.376245745725</v>
+        <v>1466.971511357417</v>
       </c>
     </row>
     <row r="12">
@@ -5114,22 +5114,22 @@
         <v>419.6213981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>831.5642142372474</v>
+        <v>679.141444343923</v>
       </c>
       <c r="L12" t="n">
-        <v>1325.664675832448</v>
+        <v>1173.241905939123</v>
       </c>
       <c r="M12" t="n">
-        <v>1634.495217575307</v>
+        <v>1482.072447681982</v>
       </c>
       <c r="N12" t="n">
-        <v>1786.701204729125</v>
+        <v>1838.102732289551</v>
       </c>
       <c r="O12" t="n">
-        <v>2248.493656412844</v>
+        <v>2299.895183973269</v>
       </c>
       <c r="P12" t="n">
-        <v>2583.773000882351</v>
+        <v>2635.174528442776</v>
       </c>
       <c r="Q12" t="n">
         <v>2635.174528442776</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>177.4315880782802</v>
+        <v>117.136538130973</v>
       </c>
       <c r="C13" t="n">
-        <v>177.4315880782802</v>
+        <v>68.92921828446326</v>
       </c>
       <c r="D13" t="n">
-        <v>177.4315880782802</v>
+        <v>68.92921828446326</v>
       </c>
       <c r="E13" t="n">
-        <v>177.4315880782802</v>
+        <v>68.92921828446326</v>
       </c>
       <c r="F13" t="n">
-        <v>177.4315880782802</v>
+        <v>68.92921828446326</v>
       </c>
       <c r="G13" t="n">
-        <v>177.4315880782802</v>
+        <v>68.92921828446326</v>
       </c>
       <c r="H13" t="n">
-        <v>173.6223697938169</v>
+        <v>65.12</v>
       </c>
       <c r="I13" t="n">
-        <v>221.5052487298998</v>
+        <v>113.0028789360829</v>
       </c>
       <c r="J13" t="n">
-        <v>409.3389893823512</v>
+        <v>300.8366195885342</v>
       </c>
       <c r="K13" t="n">
-        <v>409.3389893823512</v>
+        <v>300.8366195885342</v>
       </c>
       <c r="L13" t="n">
-        <v>409.3389893823512</v>
+        <v>300.8366195885342</v>
       </c>
       <c r="M13" t="n">
-        <v>409.3389893823512</v>
+        <v>300.8366195885342</v>
       </c>
       <c r="N13" t="n">
-        <v>409.3389893823512</v>
+        <v>300.8366195885342</v>
       </c>
       <c r="O13" t="n">
-        <v>409.3389893823512</v>
+        <v>67.92126606225077</v>
       </c>
       <c r="P13" t="n">
-        <v>409.3389893823512</v>
+        <v>67.92126606225077</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.12</v>
+        <v>67.92126606225077</v>
       </c>
       <c r="R13" t="n">
-        <v>65.12</v>
+        <v>67.92126606225077</v>
       </c>
       <c r="S13" t="n">
-        <v>65.12</v>
+        <v>67.92126606225077</v>
       </c>
       <c r="T13" t="n">
-        <v>79.94567915880486</v>
+        <v>82.74694522105563</v>
       </c>
       <c r="U13" t="n">
-        <v>153.2468717970915</v>
+        <v>156.0481378593423</v>
       </c>
       <c r="V13" t="n">
-        <v>178.8182646830375</v>
+        <v>181.6195307452882</v>
       </c>
       <c r="W13" t="n">
-        <v>177.4315880782802</v>
+        <v>180.232854140531</v>
       </c>
       <c r="X13" t="n">
-        <v>177.4315880782802</v>
+        <v>180.232854140531</v>
       </c>
       <c r="Y13" t="n">
-        <v>177.4315880782802</v>
+        <v>117.136538130973</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>653.4059340138207</v>
+        <v>1049.800488169968</v>
       </c>
       <c r="C14" t="n">
-        <v>452.9265620512006</v>
+        <v>849.3211162073476</v>
       </c>
       <c r="D14" t="n">
-        <v>291.9779198897361</v>
+        <v>688.3724740458831</v>
       </c>
       <c r="E14" t="n">
-        <v>291.9779198897361</v>
+        <v>533.4600603015713</v>
       </c>
       <c r="F14" t="n">
-        <v>136.5338504877039</v>
+        <v>378.015990899539</v>
       </c>
       <c r="G14" t="n">
-        <v>136.5338504877039</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="H14" t="n">
         <v>65.12</v>
@@ -5272,22 +5272,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>887.4717564436343</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1693.331756443634</v>
+        <v>1262.289113037656</v>
       </c>
       <c r="M14" t="n">
-        <v>2204.180585172569</v>
+        <v>1773.137941766591</v>
       </c>
       <c r="N14" t="n">
-        <v>2817.400904947332</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="O14" t="n">
-        <v>2817.400904947332</v>
+        <v>3192.218261541354</v>
       </c>
       <c r="P14" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="Q14" t="n">
         <v>3256</v>
@@ -5299,22 +5299,22 @@
         <v>3009.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>2670.622475221327</v>
+        <v>3009.688719391593</v>
       </c>
       <c r="U14" t="n">
-        <v>2268.378741333841</v>
+        <v>2607.444985504108</v>
       </c>
       <c r="V14" t="n">
-        <v>1885.70093914513</v>
+        <v>2224.767183315396</v>
       </c>
       <c r="W14" t="n">
-        <v>1494.414599770435</v>
+        <v>1890.809153926582</v>
       </c>
       <c r="X14" t="n">
-        <v>1149.68547506269</v>
+        <v>1546.080029218837</v>
       </c>
       <c r="Y14" t="n">
-        <v>886.7385733628859</v>
+        <v>1283.133127519033</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>65.12</v>
       </c>
       <c r="I15" t="n">
-        <v>98.65487796756496</v>
+        <v>65.12</v>
       </c>
       <c r="J15" t="n">
-        <v>222.6113981428639</v>
+        <v>437.5665201752989</v>
       </c>
       <c r="K15" t="n">
-        <v>660.2942142372473</v>
+        <v>875.2493362696823</v>
       </c>
       <c r="L15" t="n">
-        <v>1180.134675832448</v>
+        <v>1146.599797864882</v>
       </c>
       <c r="M15" t="n">
-        <v>1266.215217575307</v>
+        <v>1259.403053742589</v>
       </c>
       <c r="N15" t="n">
-        <v>1647.985502182875</v>
+        <v>1392.683338350157</v>
       </c>
       <c r="O15" t="n">
-        <v>1887.027953866594</v>
+        <v>1880.215790033876</v>
       </c>
       <c r="P15" t="n">
-        <v>2164.093606942957</v>
+        <v>2241.235134503383</v>
       </c>
       <c r="Q15" t="n">
         <v>2241.235134503383</v>
@@ -5406,49 +5406,49 @@
         <v>283.9399739669084</v>
       </c>
       <c r="C16" t="n">
-        <v>283.9399739669084</v>
+        <v>261.9952803830249</v>
       </c>
       <c r="D16" t="n">
-        <v>283.9399739669084</v>
+        <v>261.9952803830249</v>
       </c>
       <c r="E16" t="n">
-        <v>283.9399739669084</v>
+        <v>261.9952803830249</v>
       </c>
       <c r="F16" t="n">
-        <v>283.9399739669084</v>
+        <v>261.9952803830249</v>
       </c>
       <c r="G16" t="n">
-        <v>289.8365398537936</v>
+        <v>267.8918462699101</v>
       </c>
       <c r="H16" t="n">
-        <v>311.8431250131912</v>
+        <v>289.8984314293077</v>
       </c>
       <c r="I16" t="n">
-        <v>385.4660039492741</v>
+        <v>363.5213103653906</v>
       </c>
       <c r="J16" t="n">
-        <v>599.0397446017254</v>
+        <v>577.0950510178419</v>
       </c>
       <c r="K16" t="n">
-        <v>599.0397446017254</v>
+        <v>577.0950510178419</v>
       </c>
       <c r="L16" t="n">
-        <v>599.0397446017254</v>
+        <v>402.8045175251357</v>
       </c>
       <c r="M16" t="n">
-        <v>599.0397446017254</v>
+        <v>402.8045175251357</v>
       </c>
       <c r="N16" t="n">
-        <v>599.0397446017254</v>
+        <v>79.38524957393878</v>
       </c>
       <c r="O16" t="n">
-        <v>599.0397446017254</v>
+        <v>79.38524957393878</v>
       </c>
       <c r="P16" t="n">
-        <v>599.0397446017254</v>
+        <v>65.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>545.5261898799506</v>
+        <v>65.12</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5488,16 +5488,16 @@
         <v>707.4720165966545</v>
       </c>
       <c r="D17" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.4503343338824</v>
+        <v>321.0153761373309</v>
       </c>
       <c r="G17" t="n">
-        <v>195.4327865692196</v>
+        <v>194.9978283726681</v>
       </c>
       <c r="H17" t="n">
         <v>65.12</v>
@@ -5506,25 +5506,25 @@
         <v>65.12</v>
       </c>
       <c r="J17" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>774.8263663478684</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1580.686366347868</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M17" t="n">
-        <v>2091.535195076804</v>
+        <v>1644.28</v>
       </c>
       <c r="N17" t="n">
-        <v>2704.755514851567</v>
+        <v>1644.28</v>
       </c>
       <c r="O17" t="n">
-        <v>2817.400904947332</v>
+        <v>2450.14</v>
       </c>
       <c r="P17" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5585,25 +5585,25 @@
         <v>126.374877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>526.5413981428638</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>715.7342142372472</v>
+        <v>698.4996261621045</v>
       </c>
       <c r="L18" t="n">
-        <v>987.0846758324474</v>
+        <v>1246.060087757305</v>
       </c>
       <c r="M18" t="n">
-        <v>1073.165217575307</v>
+        <v>1332.140629500164</v>
       </c>
       <c r="N18" t="n">
-        <v>1206.445502182875</v>
+        <v>1465.420914107732</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.601838231026</v>
+        <v>1704.463365791451</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5670,25 +5670,25 @@
         <v>859.3027230120967</v>
       </c>
       <c r="L19" t="n">
-        <v>713.2950178022188</v>
+        <v>842.7901630376691</v>
       </c>
       <c r="M19" t="n">
-        <v>469.2226830521684</v>
+        <v>842.7901630376691</v>
       </c>
       <c r="N19" t="n">
-        <v>174.0862433837998</v>
+        <v>842.7901630376691</v>
       </c>
       <c r="O19" t="n">
-        <v>174.0862433837998</v>
+        <v>477.6936336649268</v>
       </c>
       <c r="P19" t="n">
-        <v>174.0862433837998</v>
+        <v>65.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>174.0862433837998</v>
+        <v>65.12</v>
       </c>
       <c r="R19" t="n">
-        <v>149.3356360634903</v>
+        <v>65.12</v>
       </c>
       <c r="S19" t="n">
         <v>65.12</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>880.1035184729978</v>
+        <v>879.6685602765009</v>
       </c>
       <c r="C20" t="n">
-        <v>707.906974793206</v>
+        <v>707.4720165967091</v>
       </c>
       <c r="D20" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180729</v>
       </c>
       <c r="E20" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565894</v>
       </c>
       <c r="F20" t="n">
         <v>321.4503343338824</v>
@@ -5743,52 +5743,52 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>774.8263663478684</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>774.8263663478684</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M20" t="n">
-        <v>1285.675195076803</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N20" t="n">
-        <v>1898.895514851567</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="O20" t="n">
-        <v>2704.755514851567</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>3256</v>
       </c>
       <c r="R20" t="n">
-        <v>3256</v>
+        <v>3256.000000000055</v>
       </c>
       <c r="S20" t="n">
-        <v>3038.406505870973</v>
+        <v>3037.971547674476</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131787037</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.22722618238</v>
       </c>
       <c r="V20" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276497</v>
       </c>
       <c r="W20" t="n">
-        <v>1636.263699381128</v>
+        <v>1635.828741184631</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759714</v>
       </c>
       <c r="Y20" t="n">
-        <v>1085.153329539235</v>
+        <v>1084.718371342738</v>
       </c>
     </row>
     <row r="21">
@@ -5819,25 +5819,25 @@
         <v>65.12</v>
       </c>
       <c r="I21" t="n">
-        <v>109.1402898924221</v>
+        <v>65.12</v>
       </c>
       <c r="J21" t="n">
-        <v>233.0968100677211</v>
+        <v>465.2865201752989</v>
       </c>
       <c r="K21" t="n">
-        <v>422.2896261621045</v>
+        <v>654.4793362696823</v>
       </c>
       <c r="L21" t="n">
-        <v>969.8500877573047</v>
+        <v>925.8297978648825</v>
       </c>
       <c r="M21" t="n">
-        <v>1332.140629500164</v>
+        <v>1288.120339607742</v>
       </c>
       <c r="N21" t="n">
-        <v>1465.420914107732</v>
+        <v>1421.40062421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1704.463365791451</v>
+        <v>1660.443075899029</v>
       </c>
       <c r="P21" t="n">
         <v>1816.992710260958</v>
@@ -5916,13 +5916,13 @@
         <v>859.3027230120967</v>
       </c>
       <c r="O22" t="n">
-        <v>859.3027230120967</v>
+        <v>516.472794369291</v>
       </c>
       <c r="P22" t="n">
-        <v>859.3027230120967</v>
+        <v>516.472794369291</v>
       </c>
       <c r="Q22" t="n">
-        <v>517.2433615971223</v>
+        <v>65.12</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>879.6685602765154</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C23" t="n">
-        <v>707.4720165967236</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D23" t="n">
-        <v>574.8062027180874</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E23" t="n">
-        <v>448.1766172566039</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F23" t="n">
-        <v>321.0153761374</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G23" t="n">
-        <v>194.9978283727372</v>
+        <v>195.4327865692196</v>
       </c>
       <c r="H23" t="n">
         <v>65.12</v>
@@ -5980,19 +5980,19 @@
         <v>65.12</v>
       </c>
       <c r="J23" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K23" t="n">
-        <v>456.4291130376557</v>
+        <v>81.61175644363432</v>
       </c>
       <c r="L23" t="n">
-        <v>1205.680904947332</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="M23" t="n">
-        <v>1205.680904947332</v>
+        <v>1398.320585172569</v>
       </c>
       <c r="N23" t="n">
-        <v>1205.680904947332</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O23" t="n">
         <v>2011.540904947332</v>
@@ -6004,28 +6004,28 @@
         <v>3256</v>
       </c>
       <c r="R23" t="n">
-        <v>3256.000000000069</v>
+        <v>3256</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.97154767449</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131787052</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182395</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V23" t="n">
-        <v>1998.832252276512</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W23" t="n">
-        <v>1635.828741184645</v>
+        <v>1635.828741184576</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.382444759729</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y23" t="n">
-        <v>1084.718371342752</v>
+        <v>1084.718371342683</v>
       </c>
     </row>
     <row r="24">
@@ -6059,19 +6059,19 @@
         <v>65.12</v>
       </c>
       <c r="J24" t="n">
-        <v>465.2865201752989</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>654.4793362696823</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L24" t="n">
         <v>925.8297978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>1011.910339607742</v>
+        <v>1288.120339607742</v>
       </c>
       <c r="N24" t="n">
-        <v>1145.19062421531</v>
+        <v>1421.40062421531</v>
       </c>
       <c r="O24" t="n">
         <v>1660.443075899029</v>
@@ -6156,10 +6156,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3027230120967</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="Q25" t="n">
-        <v>407.9499286428058</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253.1649250963515</v>
+        <v>1079.65431918501</v>
       </c>
       <c r="C26" t="n">
-        <v>61.84</v>
+        <v>852.9123209597633</v>
       </c>
       <c r="D26" t="n">
-        <v>61.84</v>
+        <v>665.7010525356726</v>
       </c>
       <c r="E26" t="n">
-        <v>61.84</v>
+        <v>484.5260125287346</v>
       </c>
       <c r="F26" t="n">
-        <v>61.84</v>
+        <v>302.8193168640761</v>
       </c>
       <c r="G26" t="n">
-        <v>61.84</v>
+        <v>122.2563145539587</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6220,19 +6220,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>963.9979417665908</v>
+        <v>1673.704308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>1577.218261541354</v>
+        <v>2286.924627889222</v>
       </c>
       <c r="O26" t="n">
-        <v>1888.130904947305</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>2653.400904947332</v>
@@ -6253,16 +6253,16 @@
         <v>1999.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>1590.510435278166</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="W26" t="n">
-        <v>1172.961469640845</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="X26" t="n">
-        <v>801.9697186704736</v>
+        <v>1628.459112759132</v>
       </c>
       <c r="Y26" t="n">
-        <v>512.760190708043</v>
+        <v>1339.249584796701</v>
       </c>
     </row>
     <row r="27">
@@ -6293,22 +6293,22 @@
         <v>61.84</v>
       </c>
       <c r="I27" t="n">
-        <v>69.63487796756496</v>
+        <v>61.84</v>
       </c>
       <c r="J27" t="n">
-        <v>416.3413981428639</v>
+        <v>408.546520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>828.2842142372474</v>
+        <v>820.4893362696823</v>
       </c>
       <c r="L27" t="n">
-        <v>1322.384675832448</v>
+        <v>1118.560378378698</v>
       </c>
       <c r="M27" t="n">
-        <v>1631.215217575307</v>
+        <v>1427.390920121557</v>
       </c>
       <c r="N27" t="n">
-        <v>1987.245502182875</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O27" t="n">
         <v>2245.213656412845</v>
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174.1515880782802</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="C28" t="n">
-        <v>174.1515880782802</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="D28" t="n">
-        <v>174.1515880782802</v>
+        <v>122.1955868066416</v>
       </c>
       <c r="E28" t="n">
-        <v>174.1515880782802</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="F28" t="n">
-        <v>174.1515880782802</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="G28" t="n">
-        <v>174.1515880782802</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="H28" t="n">
-        <v>170.342369793817</v>
+        <v>61.84</v>
       </c>
       <c r="I28" t="n">
-        <v>218.2252487298999</v>
+        <v>109.7228789360829</v>
       </c>
       <c r="J28" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="K28" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="L28" t="n">
-        <v>406.0589893823512</v>
+        <v>97.0034598332017</v>
       </c>
       <c r="M28" t="n">
-        <v>406.0589893823512</v>
+        <v>71.03169373397299</v>
       </c>
       <c r="N28" t="n">
-        <v>406.0589893823512</v>
+        <v>71.03169373397299</v>
       </c>
       <c r="O28" t="n">
-        <v>406.0589893823512</v>
+        <v>71.03169373397299</v>
       </c>
       <c r="P28" t="n">
-        <v>406.0589893823512</v>
+        <v>71.03169373397299</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>71.03169373397299</v>
       </c>
       <c r="R28" t="n">
-        <v>61.84</v>
+        <v>71.03169373397299</v>
       </c>
       <c r="S28" t="n">
-        <v>61.84</v>
+        <v>71.03169373397299</v>
       </c>
       <c r="T28" t="n">
-        <v>76.66567915880486</v>
+        <v>85.85737289277785</v>
       </c>
       <c r="U28" t="n">
-        <v>149.9668717970915</v>
+        <v>159.1585655310645</v>
       </c>
       <c r="V28" t="n">
-        <v>175.5382646830375</v>
+        <v>184.7299584170105</v>
       </c>
       <c r="W28" t="n">
-        <v>174.1515880782802</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="X28" t="n">
-        <v>174.1515880782802</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="Y28" t="n">
-        <v>174.1515880782802</v>
+        <v>183.3432818122532</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>288.5819982252464</v>
+        <v>670.7138907336723</v>
       </c>
       <c r="C29" t="n">
-        <v>61.84</v>
+        <v>443.9718925084259</v>
       </c>
       <c r="D29" t="n">
-        <v>61.84</v>
+        <v>256.7606240843352</v>
       </c>
       <c r="E29" t="n">
-        <v>61.84</v>
+        <v>242.4030023101174</v>
       </c>
       <c r="F29" t="n">
-        <v>61.84</v>
+        <v>242.4030023101174</v>
       </c>
       <c r="G29" t="n">
         <v>61.84</v>
@@ -6454,25 +6454,25 @@
         <v>61.84</v>
       </c>
       <c r="J29" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K29" t="n">
-        <v>453.1491130376558</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L29" t="n">
-        <v>453.1491130376558</v>
+        <v>1536.816366347868</v>
       </c>
       <c r="M29" t="n">
-        <v>963.9979417665908</v>
+        <v>1561.459999999933</v>
       </c>
       <c r="N29" t="n">
-        <v>1577.218261541354</v>
+        <v>1561.459999999933</v>
       </c>
       <c r="O29" t="n">
-        <v>2342.488261541389</v>
+        <v>2326.729999999966</v>
       </c>
       <c r="P29" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q29" t="n">
         <v>3092</v>
@@ -6481,25 +6481,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>2828.703167441403</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>2463.37429700851</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2034.867936858398</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V29" t="n">
-        <v>1625.927508407061</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W29" t="n">
-        <v>1208.37854276974</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="X29" t="n">
-        <v>837.3867917993684</v>
+        <v>1219.518684307795</v>
       </c>
       <c r="Y29" t="n">
-        <v>548.1772638369378</v>
+        <v>930.3091563453638</v>
       </c>
     </row>
     <row r="30">
@@ -6530,25 +6530,25 @@
         <v>61.84</v>
       </c>
       <c r="I30" t="n">
-        <v>69.63487796756496</v>
+        <v>61.84</v>
       </c>
       <c r="J30" t="n">
-        <v>212.5171006891147</v>
+        <v>408.546520175299</v>
       </c>
       <c r="K30" t="n">
-        <v>624.4599167834981</v>
+        <v>820.4893362696823</v>
       </c>
       <c r="L30" t="n">
-        <v>1118.560378378698</v>
+        <v>1314.589797864882</v>
       </c>
       <c r="M30" t="n">
-        <v>1427.390920121557</v>
+        <v>1623.420339607742</v>
       </c>
       <c r="N30" t="n">
-        <v>1783.421204729126</v>
+        <v>1979.45062421531</v>
       </c>
       <c r="O30" t="n">
-        <v>2245.213656412845</v>
+        <v>2441.243075899029</v>
       </c>
       <c r="P30" t="n">
         <v>2580.493000882351</v>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>174.1515880782802</v>
+        <v>112.7970522213419</v>
       </c>
       <c r="C31" t="n">
-        <v>174.1515880782802</v>
+        <v>112.7970522213419</v>
       </c>
       <c r="D31" t="n">
-        <v>174.1515880782802</v>
+        <v>112.7970522213419</v>
       </c>
       <c r="E31" t="n">
-        <v>174.1515880782802</v>
+        <v>112.7970522213419</v>
       </c>
       <c r="F31" t="n">
-        <v>174.1515880782802</v>
+        <v>112.7970522213419</v>
       </c>
       <c r="G31" t="n">
-        <v>174.1515880782802</v>
+        <v>112.7970522213419</v>
       </c>
       <c r="H31" t="n">
-        <v>170.342369793817</v>
+        <v>112.7970522213419</v>
       </c>
       <c r="I31" t="n">
-        <v>218.2252487298999</v>
+        <v>160.6799311574248</v>
       </c>
       <c r="J31" t="n">
-        <v>406.0589893823512</v>
+        <v>348.5136718098761</v>
       </c>
       <c r="K31" t="n">
-        <v>406.0589893823512</v>
+        <v>348.5136718098761</v>
       </c>
       <c r="L31" t="n">
-        <v>360.457789295505</v>
+        <v>348.5136718098761</v>
       </c>
       <c r="M31" t="n">
-        <v>61.84</v>
+        <v>348.5136718098761</v>
       </c>
       <c r="N31" t="n">
-        <v>61.84</v>
+        <v>348.5136718098761</v>
       </c>
       <c r="O31" t="n">
-        <v>61.84</v>
+        <v>348.5136718098761</v>
       </c>
       <c r="P31" t="n">
-        <v>61.84</v>
+        <v>348.5136718098761</v>
       </c>
       <c r="Q31" t="n">
         <v>61.84</v>
@@ -6651,13 +6651,13 @@
         <v>175.5382646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="X31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="Y31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
     </row>
     <row r="32">
@@ -6694,22 +6694,22 @@
         <v>61.84</v>
       </c>
       <c r="K32" t="n">
-        <v>771.3406764391793</v>
+        <v>771.3406764391789</v>
       </c>
       <c r="L32" t="n">
-        <v>966.8649854353201</v>
+        <v>755.8025956310979</v>
       </c>
       <c r="M32" t="n">
-        <v>951.3269046272384</v>
+        <v>1261.485644023032</v>
       </c>
       <c r="N32" t="n">
-        <v>1561.459999999917</v>
+        <v>1245.94756321495</v>
       </c>
       <c r="O32" t="n">
-        <v>2326.729999999959</v>
+        <v>2011.217563214991</v>
       </c>
       <c r="P32" t="n">
-        <v>3092</v>
+        <v>2660.033647533245</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
@@ -6767,28 +6767,28 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>134.974877967565</v>
+        <v>61.84</v>
       </c>
       <c r="J33" t="n">
-        <v>258.9313981428639</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>448.1242142372473</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>944.220378378698</v>
+        <v>646.3397978648825</v>
       </c>
       <c r="M33" t="n">
-        <v>1030.300920121557</v>
+        <v>1020.510339607742</v>
       </c>
       <c r="N33" t="n">
-        <v>1163.581204729126</v>
+        <v>1153.79062421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1402.623656412844</v>
+        <v>1392.833075899029</v>
       </c>
       <c r="P33" t="n">
-        <v>1515.153000882351</v>
+        <v>1631.894528442776</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6861,16 +6861,16 @@
         <v>1011.831843630703</v>
       </c>
       <c r="N34" t="n">
-        <v>1011.831843630703</v>
+        <v>902.2945710196249</v>
       </c>
       <c r="O34" t="n">
-        <v>658.8565263791725</v>
+        <v>902.2945710196249</v>
       </c>
       <c r="P34" t="n">
-        <v>258.4041048354578</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.84</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R34" t="n">
         <v>61.84</v>
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C35" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D35" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E35" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F35" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G35" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H35" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I35" t="n">
         <v>61.84</v>
@@ -6931,19 +6931,19 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>430.0181114556215</v>
+        <v>1155.056868702881</v>
       </c>
       <c r="L35" t="n">
-        <v>414.4800306475406</v>
+        <v>1139.5187878948</v>
       </c>
       <c r="M35" t="n">
-        <v>518.4380752395722</v>
+        <v>1645.201836286733</v>
       </c>
       <c r="N35" t="n">
-        <v>1129.493647533147</v>
+        <v>2255.334931659412</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533196</v>
+        <v>2675.571728341327</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -6952,28 +6952,28 @@
         <v>3092</v>
       </c>
       <c r="R35" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S35" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T35" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U35" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V35" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W35" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X35" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y35" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="36">
@@ -7004,28 +7004,28 @@
         <v>61.84</v>
       </c>
       <c r="I36" t="n">
-        <v>134.974877967565</v>
+        <v>61.84</v>
       </c>
       <c r="J36" t="n">
-        <v>258.9313981428639</v>
+        <v>312.3286282495399</v>
       </c>
       <c r="K36" t="n">
-        <v>448.1242142372473</v>
+        <v>501.5214443439232</v>
       </c>
       <c r="L36" t="n">
-        <v>719.4746758324475</v>
+        <v>1060.961905939123</v>
       </c>
       <c r="M36" t="n">
-        <v>805.5552175753068</v>
+        <v>1147.042447681983</v>
       </c>
       <c r="N36" t="n">
-        <v>938.8355021828751</v>
+        <v>1280.322732289551</v>
       </c>
       <c r="O36" t="n">
-        <v>1177.877953866594</v>
+        <v>1519.36518397327</v>
       </c>
       <c r="P36" t="n">
-        <v>1515.153000882351</v>
+        <v>1631.894528442776</v>
       </c>
       <c r="Q36" t="n">
         <v>1631.894528442776</v>
@@ -7092,25 +7092,25 @@
         <v>1011.831843630703</v>
       </c>
       <c r="L37" t="n">
-        <v>877.945350542037</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M37" t="n">
-        <v>877.945350542037</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N37" t="n">
-        <v>877.945350542037</v>
+        <v>728.8166160835463</v>
       </c>
       <c r="O37" t="n">
-        <v>877.945350542037</v>
+        <v>728.8166160835463</v>
       </c>
       <c r="P37" t="n">
-        <v>877.945350542037</v>
+        <v>728.8166160835463</v>
       </c>
       <c r="Q37" t="n">
-        <v>573.9365734181883</v>
+        <v>289.5850338354674</v>
       </c>
       <c r="R37" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7150,16 +7150,16 @@
         <v>532.0183239301398</v>
       </c>
       <c r="E38" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F38" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G38" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H38" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I38" t="n">
         <v>61.84</v>
@@ -7168,22 +7168,22 @@
         <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>430.9405883765176</v>
+        <v>1155.056868702882</v>
       </c>
       <c r="L38" t="n">
-        <v>415.4025075684366</v>
+        <v>1920.326868702882</v>
       </c>
       <c r="M38" t="n">
-        <v>921.0855559603701</v>
+        <v>1904.7887878948</v>
       </c>
       <c r="N38" t="n">
-        <v>1531.218651333048</v>
+        <v>1889.250707086718</v>
       </c>
       <c r="O38" t="n">
-        <v>2296.488651333105</v>
+        <v>2654.520707086773</v>
       </c>
       <c r="P38" t="n">
-        <v>2660.033647533246</v>
+        <v>3092</v>
       </c>
       <c r="Q38" t="n">
         <v>3092</v>
@@ -7241,25 +7241,25 @@
         <v>61.84</v>
       </c>
       <c r="I39" t="n">
-        <v>134.974877967565</v>
+        <v>61.84</v>
       </c>
       <c r="J39" t="n">
-        <v>483.6771006891146</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K39" t="n">
-        <v>672.869916783498</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L39" t="n">
-        <v>944.220378378698</v>
+        <v>646.3397978648825</v>
       </c>
       <c r="M39" t="n">
-        <v>1030.300920121557</v>
+        <v>732.4203396077418</v>
       </c>
       <c r="N39" t="n">
-        <v>1163.581204729126</v>
+        <v>865.7006242153101</v>
       </c>
       <c r="O39" t="n">
-        <v>1402.623656412844</v>
+        <v>1392.833075899029</v>
       </c>
       <c r="P39" t="n">
         <v>1515.153000882351</v>
@@ -7335,19 +7335,19 @@
         <v>645.9942279131988</v>
       </c>
       <c r="N40" t="n">
-        <v>362.9790003660423</v>
+        <v>645.9942279131988</v>
       </c>
       <c r="O40" t="n">
-        <v>133.9344239422782</v>
+        <v>645.9942279131988</v>
       </c>
       <c r="P40" t="n">
-        <v>133.9344239422782</v>
+        <v>245.5418063694841</v>
       </c>
       <c r="Q40" t="n">
-        <v>133.9344239422782</v>
+        <v>245.5418063694841</v>
       </c>
       <c r="R40" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>500.0356908917614</v>
+        <v>844.6640559983891</v>
       </c>
       <c r="C41" t="n">
-        <v>261.1724805453028</v>
+        <v>844.6640559983891</v>
       </c>
       <c r="D41" t="n">
-        <v>61.84</v>
+        <v>645.3315754530863</v>
       </c>
       <c r="E41" t="n">
-        <v>61.84</v>
+        <v>645.3315754530863</v>
       </c>
       <c r="F41" t="n">
-        <v>61.84</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="G41" t="n">
-        <v>61.84</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7402,22 +7402,22 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K41" t="n">
-        <v>1162.855479385524</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L41" t="n">
-        <v>1162.855479385524</v>
+        <v>1536.816366347868</v>
       </c>
       <c r="M41" t="n">
-        <v>1673.704308114459</v>
+        <v>1561.459999999875</v>
       </c>
       <c r="N41" t="n">
-        <v>2286.924627889222</v>
+        <v>1561.459999999875</v>
       </c>
       <c r="O41" t="n">
-        <v>2326.729999999937</v>
+        <v>2326.729999999938</v>
       </c>
       <c r="P41" t="n">
         <v>3092</v>
@@ -7426,28 +7426,28 @@
         <v>3092</v>
       </c>
       <c r="R41" t="n">
-        <v>3092</v>
+        <v>3053.738789062329</v>
       </c>
       <c r="S41" t="n">
-        <v>3092</v>
+        <v>2769.043670070084</v>
       </c>
       <c r="T41" t="n">
-        <v>2747.555262402298</v>
+        <v>2662.513449750392</v>
       </c>
       <c r="U41" t="n">
-        <v>2306.927690130974</v>
+        <v>2221.885877479068</v>
       </c>
       <c r="V41" t="n">
-        <v>1885.866049558424</v>
+        <v>1800.824236906519</v>
       </c>
       <c r="W41" t="n">
-        <v>1456.195871799891</v>
+        <v>1800.824236906519</v>
       </c>
       <c r="X41" t="n">
-        <v>1073.082908708308</v>
+        <v>1417.711273814935</v>
       </c>
       <c r="Y41" t="n">
-        <v>771.7521686246649</v>
+        <v>1116.380533731293</v>
       </c>
     </row>
     <row r="42">
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>845.0520685412207</v>
+        <v>717.136672240335</v>
       </c>
       <c r="C42" t="n">
-        <v>695.4561973841305</v>
+        <v>567.5408010832448</v>
       </c>
       <c r="D42" t="n">
-        <v>559.1555035480673</v>
+        <v>431.2401072471815</v>
       </c>
       <c r="E42" t="n">
-        <v>428.1735871622969</v>
+        <v>300.2581908614112</v>
       </c>
       <c r="F42" t="n">
         <v>300.2581908614112</v>
@@ -7484,49 +7484,49 @@
         <v>396.666520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>625.6009126690915</v>
+        <v>595.3750035424588</v>
       </c>
       <c r="L42" t="n">
-        <v>1107.821374264292</v>
+        <v>1077.595465137659</v>
       </c>
       <c r="M42" t="n">
-        <v>1404.771916007151</v>
+        <v>1374.546006880518</v>
       </c>
       <c r="N42" t="n">
-        <v>1748.922200614719</v>
+        <v>1718.696291488086</v>
       </c>
       <c r="O42" t="n">
-        <v>2198.834652298438</v>
+        <v>2168.608743171805</v>
       </c>
       <c r="P42" t="n">
-        <v>2522.233996767945</v>
+        <v>2492.008087641312</v>
       </c>
       <c r="Q42" t="n">
-        <v>2561.75552432837</v>
+        <v>2531.529615201737</v>
       </c>
       <c r="R42" t="n">
-        <v>2224.105224033037</v>
+        <v>2193.879314906404</v>
       </c>
       <c r="S42" t="n">
-        <v>2224.105224033037</v>
+        <v>1937.754062416898</v>
       </c>
       <c r="T42" t="n">
-        <v>2029.804451086053</v>
+        <v>1743.453289469914</v>
       </c>
       <c r="U42" t="n">
-        <v>1840.703077590915</v>
+        <v>1554.351915974776</v>
       </c>
       <c r="V42" t="n">
-        <v>1637.156949114632</v>
+        <v>1350.805787498493</v>
       </c>
       <c r="W42" t="n">
-        <v>1415.567915872381</v>
+        <v>1129.216754256242</v>
       </c>
       <c r="X42" t="n">
-        <v>1206.615653806333</v>
+        <v>920.264492190194</v>
       </c>
       <c r="Y42" t="n">
-        <v>1018.341519699126</v>
+        <v>731.9903580829875</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>110.1379787304532</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="C43" t="n">
-        <v>110.1379787304532</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="D43" t="n">
-        <v>110.1379787304532</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="E43" t="n">
-        <v>110.1379787304532</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="F43" t="n">
-        <v>110.1379787304532</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="G43" t="n">
-        <v>77.77043040567538</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="H43" t="n">
+        <v>123.9678342773621</v>
+      </c>
+      <c r="I43" t="n">
+        <v>159.970713213445</v>
+      </c>
+      <c r="J43" t="n">
+        <v>335.9244538658963</v>
+      </c>
+      <c r="K43" t="n">
+        <v>335.9244538658963</v>
+      </c>
+      <c r="L43" t="n">
+        <v>335.9244538658963</v>
+      </c>
+      <c r="M43" t="n">
+        <v>335.9244538658963</v>
+      </c>
+      <c r="N43" t="n">
+        <v>335.9244538658963</v>
+      </c>
+      <c r="O43" t="n">
+        <v>335.9244538658963</v>
+      </c>
+      <c r="P43" t="n">
+        <v>335.9244538658963</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>335.9244538658963</v>
+      </c>
+      <c r="R43" t="n">
         <v>61.84</v>
       </c>
-      <c r="I43" t="n">
-        <v>97.84287893608291</v>
-      </c>
-      <c r="J43" t="n">
-        <v>273.7966195885342</v>
-      </c>
-      <c r="K43" t="n">
-        <v>273.7966195885342</v>
-      </c>
-      <c r="L43" t="n">
-        <v>273.7966195885342</v>
-      </c>
-      <c r="M43" t="n">
-        <v>273.7966195885342</v>
-      </c>
-      <c r="N43" t="n">
-        <v>273.7966195885342</v>
-      </c>
-      <c r="O43" t="n">
-        <v>273.7966195885342</v>
-      </c>
-      <c r="P43" t="n">
-        <v>273.7966195885342</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>273.7966195885342</v>
-      </c>
-      <c r="R43" t="n">
-        <v>249.8690116272598</v>
-      </c>
       <c r="S43" t="n">
-        <v>98.9867088971028</v>
+        <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>101.9323880559077</v>
+        <v>64.78567915880487</v>
       </c>
       <c r="U43" t="n">
-        <v>123.6458674564226</v>
+        <v>126.2068717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>123.6458674564226</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>110.1379787304532</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="X43" t="n">
-        <v>110.1379787304532</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="Y43" t="n">
-        <v>110.1379787304532</v>
+        <v>139.8982646830375</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>205.6894836373359</v>
+        <v>1434.399276048755</v>
       </c>
       <c r="C44" t="n">
-        <v>205.6894836373359</v>
+        <v>1169.273439439671</v>
       </c>
       <c r="D44" t="n">
-        <v>205.6894836373359</v>
+        <v>943.6783326317416</v>
       </c>
       <c r="E44" t="n">
-        <v>205.6894836373359</v>
+        <v>724.1194542409652</v>
       </c>
       <c r="F44" t="n">
-        <v>205.6894836373359</v>
+        <v>504.0289201924683</v>
       </c>
       <c r="G44" t="n">
-        <v>61.84</v>
+        <v>285.0820794985125</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7639,52 +7639,52 @@
         <v>61.84</v>
       </c>
       <c r="J44" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K44" t="n">
-        <v>1162.855479385524</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L44" t="n">
-        <v>1928.125479385524</v>
+        <v>1536.816366347868</v>
       </c>
       <c r="M44" t="n">
-        <v>2438.974308114459</v>
+        <v>2047.665195076803</v>
       </c>
       <c r="N44" t="n">
-        <v>3052.194627889222</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3027.476162799703</v>
+        <v>3092</v>
       </c>
       <c r="S44" t="n">
-        <v>2716.518417544831</v>
+        <v>2781.042254745129</v>
       </c>
       <c r="T44" t="n">
-        <v>2312.8057087281</v>
+        <v>2377.329545928397</v>
       </c>
       <c r="U44" t="n">
-        <v>1845.91551019415</v>
+        <v>2377.329545928397</v>
       </c>
       <c r="V44" t="n">
-        <v>1398.591243358974</v>
+        <v>1930.005279093222</v>
       </c>
       <c r="W44" t="n">
-        <v>942.6584393378148</v>
+        <v>1474.072475072062</v>
       </c>
       <c r="X44" t="n">
-        <v>533.2828499836049</v>
+        <v>1474.072475072062</v>
       </c>
       <c r="Y44" t="n">
-        <v>205.6894836373359</v>
+        <v>1474.072475072062</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>565.5511234700211</v>
+        <v>1683.41065471734</v>
       </c>
       <c r="C45" t="n">
-        <v>565.5511234700211</v>
+        <v>1507.552157297624</v>
       </c>
       <c r="D45" t="n">
-        <v>533.2240922128019</v>
+        <v>1344.988837198934</v>
       </c>
       <c r="E45" t="n">
-        <v>533.2240922128019</v>
+        <v>1187.744294550538</v>
       </c>
       <c r="F45" t="n">
-        <v>379.04606964929</v>
+        <v>1033.566271987026</v>
       </c>
       <c r="G45" t="n">
-        <v>238.9051243209795</v>
+        <v>893.4253266587152</v>
       </c>
       <c r="H45" t="n">
-        <v>92.27069281954398</v>
+        <v>746.7908951572797</v>
       </c>
       <c r="I45" t="n">
-        <v>61.84</v>
+        <v>746.7908951572797</v>
       </c>
       <c r="J45" t="n">
-        <v>370.9265201752989</v>
+        <v>1055.877415332579</v>
       </c>
       <c r="K45" t="n">
-        <v>745.2493362696823</v>
+        <v>1324.066915901147</v>
       </c>
       <c r="L45" t="n">
-        <v>1035.42048025587</v>
+        <v>1780.547377496347</v>
       </c>
       <c r="M45" t="n">
-        <v>1306.631021998729</v>
+        <v>2051.757919239206</v>
       </c>
       <c r="N45" t="n">
-        <v>1625.041306606297</v>
+        <v>2370.168203846774</v>
       </c>
       <c r="O45" t="n">
-        <v>2049.213758290016</v>
+        <v>2794.340655530493</v>
       </c>
       <c r="P45" t="n">
-        <v>2346.873102759523</v>
+        <v>3092</v>
       </c>
       <c r="Q45" t="n">
-        <v>2360.654630319948</v>
+        <v>3092</v>
       </c>
       <c r="R45" t="n">
-        <v>1996.741703761989</v>
+        <v>2728.087073442041</v>
       </c>
       <c r="S45" t="n">
-        <v>1714.353825009856</v>
+        <v>2728.087073442041</v>
       </c>
       <c r="T45" t="n">
-        <v>1493.790425800246</v>
+        <v>2507.523674232431</v>
       </c>
       <c r="U45" t="n">
-        <v>1278.426426042482</v>
+        <v>2292.159674474667</v>
       </c>
       <c r="V45" t="n">
-        <v>1048.617671303573</v>
+        <v>2062.350919735758</v>
       </c>
       <c r="W45" t="n">
-        <v>800.7660117986954</v>
+        <v>2062.350919735758</v>
       </c>
       <c r="X45" t="n">
-        <v>565.5511234700211</v>
+        <v>1897.947415087173</v>
       </c>
       <c r="Y45" t="n">
-        <v>565.5511234700211</v>
+        <v>1683.41065471734</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="C46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="D46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="E46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="F46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="G46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="H46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="I46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="J46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="K46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="L46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="M46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="N46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="O46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="P46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="R46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="S46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="T46" t="n">
         <v>61.84</v>
       </c>
-      <c r="I46" t="n">
-        <v>72.10287893608292</v>
-      </c>
-      <c r="J46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="K46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="L46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="M46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="N46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="O46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="P46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="R46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="S46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="T46" t="n">
-        <v>120.4156216612533</v>
-      </c>
       <c r="U46" t="n">
-        <v>156.0968142995399</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="V46" t="n">
-        <v>143.8035716568973</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="W46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="X46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="Y46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
     </row>
   </sheetData>
@@ -7967,7 +7967,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7979,13 +7979,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>814.2870600406815</v>
+        <v>501.1325584305586</v>
       </c>
       <c r="Q2" t="n">
-        <v>399.8224541363521</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>113.6762873319659</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
         <v>884.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>782.7350356674784</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q5" t="n">
-        <v>615.8520732695737</v>
+        <v>189.0212843274853</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>163.033511207844</v>
+        <v>500.8454983898772</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>435.3966095009885</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,10 +8690,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>505.6444790750808</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8915,7 +8915,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>435.3966095009885</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>814</v>
@@ -8927,13 +8927,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>64.71305848375822</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>1027.236390889262</v>
       </c>
       <c r="N17" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
-        <v>184.0310918930479</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>884.2478695740924</v>
+        <v>408.1838259709342</v>
       </c>
       <c r="P20" t="n">
-        <v>557.0996713017253</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,22 +9623,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>16.65833984205487</v>
       </c>
       <c r="L23" t="n">
-        <v>756.8199918279561</v>
+        <v>814</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
         <v>814.2870600406815</v>
@@ -9863,7 +9863,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9875,10 +9875,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>384.301044731619</v>
+        <v>440.4259272085471</v>
       </c>
       <c r="P26" t="n">
-        <v>773.287060040709</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>569.1546868868268</v>
       </c>
       <c r="N29" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O29" t="n">
-        <v>843.2478695741272</v>
+        <v>843.2478695741263</v>
       </c>
       <c r="P29" t="n">
-        <v>314.3402351982006</v>
+        <v>773.2870600407153</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,22 +10340,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>208.9517659061795</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741345</v>
+        <v>843.2478695741336</v>
       </c>
       <c r="P32" t="n">
-        <v>773.2870600407235</v>
+        <v>657.9976835157544</v>
       </c>
       <c r="Q32" t="n">
-        <v>188.2053843274865</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>662.5632917884294</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>843.2478695741418</v>
+        <v>501.6649982891891</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407308</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10811,25 +10811,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>773.0000000000002</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>843.247869574149</v>
+        <v>843.2478695741481</v>
       </c>
       <c r="P38" t="n">
-        <v>375.5793062788223</v>
+        <v>448.7742600247773</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>188.2053843274866</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,25 +11045,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>569.1546868867689</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>110.4553161505717</v>
+        <v>843.2478695741554</v>
       </c>
       <c r="P41" t="n">
-        <v>773.2870600407454</v>
+        <v>773.2870600407444</v>
       </c>
       <c r="Q41" t="n">
         <v>172.8226843274854</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>773</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1096.663422488788</v>
+        <v>1089.103210464309</v>
       </c>
       <c r="O44" t="n">
-        <v>110.4553161506355</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,10 +22700,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>29.21007785423346</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>5.662449696444753</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22937,10 +22937,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.662449696446828</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>29.21007785422375</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>5.662449696447055</v>
+        <v>5.662449696447041</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23223,7 +23223,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -23280,16 +23280,16 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.653898001264622</v>
       </c>
       <c r="V11" t="n">
-        <v>111.9364185063578</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -23384,7 +23384,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>60.53621805555548</v>
@@ -23420,13 +23420,13 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>415.445564079015</v>
+        <v>184.8593640879943</v>
       </c>
       <c r="P13" t="n">
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
         <v>501.6021279811511</v>
@@ -23450,7 +23450,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>152.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>86.30994672070057</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23514,7 +23514,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -23523,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>56.75502688602182</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -23621,7 +23621,7 @@
         <v>36.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>21.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>34.53621805555548</v>
@@ -23648,25 +23648,25 @@
         <v>37.52077380114304</v>
       </c>
       <c r="L16" t="n">
-        <v>172.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>320.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>422.3253002500781</v>
       </c>
       <c r="Q16" t="n">
-        <v>421.860847251041</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23703,7 +23703,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4306086145859638</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -23715,7 +23715,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.4306086145860206</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23885,28 +23885,28 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>128.2001937830958</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>423.0990267340447</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.4306086145264487</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.430608614585708</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24131,16 +24131,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>361.445564079015</v>
+        <v>22.04393472263729</v>
       </c>
       <c r="P22" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>108.2004986247733</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.4306086145786878</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4306086145176096</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24371,13 +24371,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>69.8091295274528</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>108.2004986247733</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>35.06290239760591</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>123.1975072951083</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24468,10 +24468,10 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24572,10 +24572,10 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>49.38285596774193</v>
@@ -24596,10 +24596,10 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>269.9195629643135</v>
       </c>
       <c r="N28" t="n">
         <v>346.1850752716849</v>
@@ -24611,7 +24611,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>501.6021279811511</v>
@@ -24651,16 +24651,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>165.149244050393</v>
       </c>
       <c r="F29" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>183.0096587035274</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>35.06290239760617</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24708,7 +24708,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -24803,7 +24803,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>47.72524664804467</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24833,10 +24833,10 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L31" t="n">
-        <v>153.4024400718014</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
         <v>346.1850752716849</v>
@@ -24848,7 +24848,7 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>500.839266425598</v>
+        <v>217.0323313338207</v>
       </c>
       <c r="R31" t="n">
         <v>501.6021279811511</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
@@ -25076,19 +25076,19 @@
         <v>229.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>280.1850752716849</v>
+        <v>171.7431753867178</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>240.2408026384948</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>71.37347970285543</v>
@@ -25307,13 +25307,13 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
         <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>349.445564079015</v>
@@ -25322,13 +25322,13 @@
         <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>133.8705770729878</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>210.1345444840383</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25550,22 +25550,22 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>122.6914334194885</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>435.6021279811511</v>
+        <v>253.7373396753618</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25596,7 +25596,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -25605,13 +25605,13 @@
         <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,13 +25641,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>37.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>281.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>32.67529150683845</v>
+        <v>268.2106636120692</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -25656,7 +25656,7 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>156.8514076621006</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -25684,7 +25684,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>126.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -25723,7 +25723,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>253.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25766,7 +25766,7 @@
         <v>61.38285596774193</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>32.04387284153003</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -25799,10 +25799,10 @@
         <v>512.839266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>489.9137960994894</v>
+        <v>242.2585186539137</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>149.3734797028554</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25814,7 +25814,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>13.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>34.44364543010755</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>294.9993129555745</v>
+        <v>255.7228459225006</v>
       </c>
       <c r="C44" t="n">
-        <v>262.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>217.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>217.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>74.34638348605372</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>221.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,7 +25878,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -25887,7 +25887,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>462.2212965486107</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -25896,10 +25896,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>324.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25912,13 +25912,13 @@
         <v>197.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>174.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>128.9339259530556</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>155.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -25930,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>30.12638589134853</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25960,7 +25960,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>279.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25972,13 +25972,13 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>70.10326984328873</v>
       </c>
       <c r="Y45" t="n">
-        <v>212.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26051,7 +26051,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>894981.5692810422</v>
+        <v>894981.5692810421</v>
       </c>
     </row>
     <row r="3">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3782747.714851019</v>
+        <v>3782747.71485102</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4514241.310399102</v>
+        <v>4514241.310399103</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5245734.905947183</v>
+        <v>5245734.905947188</v>
       </c>
     </row>
     <row r="9">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7309711.176542766</v>
+        <v>7309711.176542768</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8046667.961566051</v>
+        <v>8046667.961566053</v>
       </c>
     </row>
     <row r="13">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9517900.485080721</v>
+        <v>9517900.485080725</v>
       </c>
     </row>
     <row r="15">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1447477.398233708</v>
+        <v>1447477.398233707</v>
       </c>
       <c r="C2" t="n">
         <v>1447477.398233707</v>
@@ -26287,10 +26287,10 @@
         <v>1402029.391467165</v>
       </c>
       <c r="H2" t="n">
+        <v>1402029.39146717</v>
+      </c>
+      <c r="I2" t="n">
         <v>1402029.391467165</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1402029.391467171</v>
       </c>
       <c r="J2" t="n">
         <v>1280368.19062423</v>
@@ -26308,10 +26308,10 @@
         <v>1409931.16836822</v>
       </c>
       <c r="O2" t="n">
-        <v>1242152.287210232</v>
+        <v>1242152.287210233</v>
       </c>
       <c r="P2" t="n">
-        <v>1158599.78752414</v>
+        <v>1158599.787524139</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575615.820517953</v>
+        <v>580502.372390945</v>
       </c>
       <c r="C4" t="n">
-        <v>573863.9117786936</v>
+        <v>578750.4636516855</v>
       </c>
       <c r="D4" t="n">
-        <v>572109.6264658828</v>
+        <v>576996.1783388748</v>
       </c>
       <c r="E4" t="n">
-        <v>493887.8206072089</v>
+        <v>498724.2862854869</v>
       </c>
       <c r="F4" t="n">
-        <v>518162.4364012046</v>
+        <v>522998.9020794826</v>
       </c>
       <c r="G4" t="n">
-        <v>542951.8445255277</v>
+        <v>547788.3102038058</v>
       </c>
       <c r="H4" t="n">
-        <v>541278.9095854306</v>
+        <v>546115.3752637112</v>
       </c>
       <c r="I4" t="n">
-        <v>539603.639201007</v>
+        <v>544440.1048792822</v>
       </c>
       <c r="J4" t="n">
-        <v>483069.4589672089</v>
+        <v>487781.687779115</v>
       </c>
       <c r="K4" t="n">
-        <v>481604.7173132672</v>
+        <v>486316.9461251733</v>
       </c>
       <c r="L4" t="n">
-        <v>543419.7365500288</v>
+        <v>548178.8299014301</v>
       </c>
       <c r="M4" t="n">
-        <v>541689.6178484762</v>
+        <v>546448.7111998776</v>
       </c>
       <c r="N4" t="n">
-        <v>539957.0115239241</v>
+        <v>544716.1048753253</v>
       </c>
       <c r="O4" t="n">
-        <v>457615.9305970518</v>
+        <v>462328.159408958</v>
       </c>
       <c r="P4" t="n">
-        <v>416810.1932019159</v>
+        <v>421522.422013822</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>502214.7777157545</v>
+        <v>497328.2258427619</v>
       </c>
       <c r="C6" t="n">
-        <v>790494.6864550132</v>
+        <v>785608.1345820213</v>
       </c>
       <c r="D6" t="n">
-        <v>792248.9717678239</v>
+        <v>787362.4198948322</v>
       </c>
       <c r="E6" t="n">
-        <v>552638.8307290213</v>
+        <v>547802.3650507433</v>
       </c>
       <c r="F6" t="n">
-        <v>738187.9468116794</v>
+        <v>733351.481133401</v>
       </c>
       <c r="G6" t="n">
-        <v>763731.0959416371</v>
+        <v>758894.6302633592</v>
       </c>
       <c r="H6" t="n">
-        <v>787804.0308817343</v>
+        <v>782967.5652034591</v>
       </c>
       <c r="I6" t="n">
-        <v>789479.3012661641</v>
+        <v>784642.8355878833</v>
       </c>
       <c r="J6" t="n">
-        <v>322488.8066570209</v>
+        <v>317776.577845115</v>
       </c>
       <c r="K6" t="n">
-        <v>712049.548310963</v>
+        <v>707337.3194990568</v>
       </c>
       <c r="L6" t="n">
-        <v>719848.9528181911</v>
+        <v>715089.8594667895</v>
       </c>
       <c r="M6" t="n">
-        <v>796779.0715197434</v>
+        <v>792019.9781683423</v>
       </c>
       <c r="N6" t="n">
-        <v>798511.6778442955</v>
+        <v>793752.5844928944</v>
       </c>
       <c r="O6" t="n">
-        <v>645231.2596131804</v>
+        <v>640519.0308012747</v>
       </c>
       <c r="P6" t="n">
-        <v>679070.2913222238</v>
+        <v>674358.0625103173</v>
       </c>
     </row>
   </sheetData>
@@ -27005,10 +27005,10 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27054,7 +27054,7 @@
         <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
@@ -27439,7 +27439,7 @@
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
@@ -27448,10 +27448,10 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>56.51176829726984</v>
+        <v>56.51176829727086</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -27496,7 +27496,7 @@
         <v>400</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X2" t="n">
         <v>400</v>
@@ -27521,16 +27521,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>315.9333609904181</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>274.4424628029984</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,19 +27591,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>333.2554937388119</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
@@ -27645,22 +27645,22 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U4" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V4" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W4" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X4" t="n">
         <v>400</v>
       </c>
-      <c r="U4" t="n">
+      <c r="Y4" t="n">
         <v>400</v>
-      </c>
-      <c r="V4" t="n">
-        <v>400</v>
-      </c>
-      <c r="W4" t="n">
-        <v>265.1144522864724</v>
-      </c>
-      <c r="X4" t="n">
-        <v>247.4436454301076</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27673,7 +27673,7 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27685,7 +27685,7 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -27752,10 +27752,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27767,7 +27767,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>222.380149700701</v>
+        <v>8.621640338997338</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27831,31 +27831,31 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
       </c>
       <c r="I7" t="n">
+        <v>176.6334556201183</v>
+      </c>
+      <c r="J7" t="n">
         <v>400</v>
       </c>
-      <c r="J7" t="n">
-        <v>35.26894883590776</v>
-      </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>272.2156529028889</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>336.3480075975918</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27913,19 +27913,19 @@
         <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>56.51176829727029</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27967,13 +27967,13 @@
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>307.3903671255645</v>
       </c>
       <c r="Y8" t="n">
         <v>400</v>
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>251.3119749597992</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28046,13 +28046,13 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>400</v>
       </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
       <c r="X9" t="n">
-        <v>326.8309322629039</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28071,28 +28071,28 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>303.4313241083931</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
         <v>400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>400</v>
-      </c>
-      <c r="G10" t="n">
-        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
-        <v>35.26894883590776</v>
+        <v>211.1760927008378</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28250,7 +28250,7 @@
         <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>71.03760616835928</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28259,7 +28259,7 @@
         <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>19.1168712588389</v>
+        <v>225</v>
       </c>
       <c r="O12" t="n">
         <v>225</v>
@@ -28268,7 +28268,7 @@
         <v>225</v>
       </c>
       <c r="Q12" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
         <v>225</v>
@@ -28481,31 +28481,31 @@
         <v>251</v>
       </c>
       <c r="I15" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J15" t="n">
         <v>251</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>251</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26.99264054024957</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>251</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>251</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>166.1982915220772</v>
-      </c>
       <c r="Q15" t="n">
-        <v>251</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>251</v>
@@ -28721,14 +28721,14 @@
         <v>279</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>261.5913251766235</v>
+      </c>
+      <c r="L18" t="n">
         <v>279</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -28736,13 +28736,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>155.6705902671033</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28867,7 +28867,7 @@
         <v>279</v>
       </c>
       <c r="F20" t="n">
-        <v>279</v>
+        <v>279.0000000000055</v>
       </c>
       <c r="G20" t="n">
         <v>279</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283496</v>
       </c>
       <c r="S20" t="n">
         <v>279</v>
@@ -28955,16 +28955,16 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
-        <v>261.5913251766234</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>279</v>
@@ -28976,7 +28976,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>44.46493928527515</v>
       </c>
       <c r="Q21" t="n">
         <v>173.0792650904796</v>
@@ -29092,7 +29092,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>279</v>
+        <v>279.0000000000073</v>
       </c>
       <c r="C23" t="n">
         <v>279</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988283643</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29195,22 +29195,22 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>279</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -29429,7 +29429,7 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
         <v>225</v>
@@ -29438,7 +29438,7 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>225</v>
+        <v>26.99048536749075</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29447,7 +29447,7 @@
         <v>225</v>
       </c>
       <c r="O27" t="n">
-        <v>19.11687125883898</v>
+        <v>225</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
@@ -29666,10 +29666,10 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J30" t="n">
         <v>225</v>
-      </c>
-      <c r="J30" t="n">
-        <v>19.11687125883917</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29687,7 +29687,7 @@
         <v>225</v>
       </c>
       <c r="P30" t="n">
-        <v>225</v>
+        <v>26.99048536749045</v>
       </c>
       <c r="Q30" t="n">
         <v>225</v>
@@ -29903,20 +29903,20 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>291</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>227.0158611578289</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
@@ -29924,10 +29924,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>127.8102101760006</v>
       </c>
       <c r="Q33" t="n">
-        <v>291</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -30061,7 +30061,7 @@
         <v>291</v>
       </c>
       <c r="I35" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S35" t="n">
         <v>291</v>
@@ -30140,17 +30140,17 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J36" t="n">
+        <v>127.8102101760009</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>291</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -30161,10 +30161,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>227.0158611578287</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>291</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30286,7 +30286,7 @@
         <v>291</v>
       </c>
       <c r="E38" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="F38" t="n">
         <v>291</v>
@@ -30298,7 +30298,7 @@
         <v>291</v>
       </c>
       <c r="I38" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30377,28 +30377,28 @@
         <v>291</v>
       </c>
       <c r="I39" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>291</v>
       </c>
-      <c r="J39" t="n">
-        <v>227.015861157829</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>9.889475266480062</v>
       </c>
       <c r="Q39" t="n">
         <v>291</v>
@@ -30620,7 +30620,7 @@
         <v>213</v>
       </c>
       <c r="K42" t="n">
-        <v>40.14300646404962</v>
+        <v>9.611785124016606</v>
       </c>
       <c r="L42" t="n">
         <v>213</v>
@@ -30729,10 +30729,10 @@
         <v>213</v>
       </c>
       <c r="U43" t="n">
-        <v>172.8911987497255</v>
+        <v>213</v>
       </c>
       <c r="V43" t="n">
-        <v>199.1703102162162</v>
+        <v>213</v>
       </c>
       <c r="W43" t="n">
         <v>213</v>
@@ -30857,10 +30857,10 @@
         <v>187</v>
       </c>
       <c r="K45" t="n">
+        <v>79.79463078200436</v>
+      </c>
+      <c r="L45" t="n">
         <v>187</v>
-      </c>
-      <c r="L45" t="n">
-        <v>19.01079029392637</v>
       </c>
       <c r="M45" t="n">
         <v>187</v>
@@ -30875,7 +30875,7 @@
         <v>187</v>
       </c>
       <c r="Q45" t="n">
-        <v>187</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
         <v>187</v>
@@ -30930,10 +30930,10 @@
         <v>187</v>
       </c>
       <c r="I46" t="n">
-        <v>187</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>107.5617575331594</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>187</v>
+        <v>186.8678665550149</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34877,19 +34877,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>60.53024709076726</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
@@ -34931,22 +34931,22 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>38.74164244776276</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34983,7 +34983,7 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -34992,7 +34992,7 @@
         <v>814</v>
       </c>
       <c r="N5" t="n">
-        <v>814</v>
+        <v>814.0000000000036</v>
       </c>
       <c r="O5" t="n">
         <v>814</v>
@@ -35117,31 +35117,31 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>121.257261628431</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>88.90436216748424</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35357,28 +35357,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>17.8951060528376</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>175.90714386493</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>435.3966095009885</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,10 +35469,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>435.3966095009883</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35536,7 +35536,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>416.1038546407913</v>
+        <v>262.1414608091506</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35545,7 +35545,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>153.7434213674937</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
         <v>466.4570219027464</v>
@@ -35554,7 +35554,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35694,7 +35694,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>435.3966095009885</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>814</v>
@@ -35706,13 +35706,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>64.42599844307681</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>33.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K15" t="n">
         <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>525.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>86.95004216450428</v>
+        <v>113.9426827047538</v>
       </c>
       <c r="N15" t="n">
-        <v>385.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>241.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>279.8642960367304</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>482.974263246945</v>
       </c>
       <c r="N17" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>113.7832223189554</v>
+        <v>814</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,13 +36007,13 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>452.6951798174147</v>
       </c>
       <c r="L18" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M18" t="n">
         <v>86.95004216450428</v>
@@ -36022,13 +36022,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>397.1276121698497</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,31 +36165,31 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>814</v>
+        <v>337.9359563968417</v>
       </c>
       <c r="P20" t="n">
-        <v>556.8126112610438</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.512089101654111e-11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36241,16 +36241,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>44.46493928527486</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K21" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>553.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
         <v>365.9500421645043</v>
@@ -36262,7 +36262,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>113.6660045146532</v>
+        <v>158.1309437999284</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36402,22 +36402,22 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>16.65833984205487</v>
       </c>
       <c r="L23" t="n">
-        <v>756.8199918279561</v>
+        <v>814</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>814</v>
@@ -36426,7 +36426,7 @@
         <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
-        <v>6.981979528761874e-11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36481,22 +36481,22 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M24" t="n">
-        <v>86.95004216450428</v>
+        <v>365.9500421645043</v>
       </c>
       <c r="N24" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
         <v>113.6660045146532</v>
@@ -36642,7 +36642,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36654,10 +36654,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>314.0531751575265</v>
+        <v>370.1780576344547</v>
       </c>
       <c r="P26" t="n">
-        <v>773.0000000000275</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>350.2086062376757</v>
@@ -36724,7 +36724,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>499.091375348687</v>
+        <v>301.0818607161777</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36733,7 +36733,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>260.5738931615854</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>24.8925592445095</v>
       </c>
       <c r="N29" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>773.0000000000348</v>
+        <v>773.0000000000339</v>
       </c>
       <c r="P29" t="n">
-        <v>314.0531751575191</v>
+        <v>773.0000000000339</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,10 +36952,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -36973,7 +36973,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>338.6660045146532</v>
+        <v>140.6564898821437</v>
       </c>
       <c r="Q30" t="n">
         <v>51.92073490952041</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320759717</v>
+        <v>727.1079320759941</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>73.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37198,10 +37198,10 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>501.1072365065158</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M33" t="n">
-        <v>86.95004216450428</v>
+        <v>377.9500421645043</v>
       </c>
       <c r="N33" t="n">
         <v>134.6265501086548</v>
@@ -37210,10 +37210,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>113.6660045146532</v>
+        <v>241.4762146906538</v>
       </c>
       <c r="Q33" t="n">
-        <v>117.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
-        <v>772.9999999999998</v>
+        <v>727.1079320760277</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="N35" t="n">
-        <v>727.1079320760458</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,16 +37426,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>73.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>125.2086062376757</v>
+        <v>253.0188164136766</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>274.091375348687</v>
+        <v>565.0913753486871</v>
       </c>
       <c r="M36" t="n">
         <v>86.95004216450428</v>
@@ -37447,10 +37447,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>340.6818656724819</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>117.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320760155</v>
+        <v>727.1079320759269</v>
       </c>
       <c r="L38" t="n">
         <v>773</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,10 +37663,10 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>73.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>352.2244673955047</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37681,10 +37681,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>241.4570219027464</v>
+        <v>532.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>113.6660045146532</v>
+        <v>123.5554797811333</v>
       </c>
       <c r="Q39" t="n">
         <v>117.9207349095204</v>
@@ -37824,25 +37824,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>24.89255924445163</v>
       </c>
       <c r="N41" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>40.20744657647921</v>
+        <v>773.000000000063</v>
       </c>
       <c r="P41" t="n">
-        <v>773.0000000000639</v>
+        <v>773.000000000063</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37906,7 +37906,7 @@
         <v>338.2086062376757</v>
       </c>
       <c r="K42" t="n">
-        <v>231.2468611048409</v>
+        <v>200.7156397648079</v>
       </c>
       <c r="L42" t="n">
         <v>487.091375348687</v>
@@ -38015,10 +38015,10 @@
         <v>2.975433493742287</v>
       </c>
       <c r="U43" t="n">
-        <v>21.93280747526759</v>
+        <v>62.04160872554206</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>13.82968978378381</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>773</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>619.4144644189528</v>
+        <v>611.854252394474</v>
       </c>
       <c r="O44" t="n">
-        <v>40.20744657654306</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,10 +38143,10 @@
         <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>378.1038546407913</v>
+        <v>270.8984854227957</v>
       </c>
       <c r="L45" t="n">
-        <v>293.1021656426134</v>
+        <v>461.091375348687</v>
       </c>
       <c r="M45" t="n">
         <v>273.9500421645043</v>
@@ -38161,7 +38161,7 @@
         <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
-        <v>13.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -38216,10 +38216,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>10.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>72.29280869725164</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>36.04160872554206</v>
+        <v>35.909475280557</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
